--- a/docs/downloads/04/tbl_other_chars_marovoay_maroala.xlsx
+++ b/docs/downloads/04/tbl_other_chars_marovoay_maroala.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -484,12 +484,6 @@
           <t>Sexe</t>
         </is>
       </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -653,14 +647,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E14">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="15">
@@ -676,14 +670,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Marié(e) religieusement</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>83</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="16">
@@ -699,20 +693,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Marié(e) selon la tradition</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D16">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="E16">
-        <v>42.6</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -722,14 +716,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Veuf(ve)</t>
+          <t>Célibataire</t>
         </is>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>348</v>
       </c>
       <c r="E17">
-        <v>3.6</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="18">
@@ -745,14 +739,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Célibataire</t>
+          <t>Divorcé(e)</t>
         </is>
       </c>
       <c r="D18">
-        <v>348</v>
+        <v>57</v>
       </c>
       <c r="E18">
-        <v>41.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="19">
@@ -768,14 +762,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Divorcé(e)</t>
+          <t>En concubinage</t>
         </is>
       </c>
       <c r="D19">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E19">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="20">
@@ -791,14 +785,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>En concubinage</t>
+          <t>Marié(e) civil / religieux / polygame</t>
         </is>
       </c>
       <c r="D20">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E20">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="21">
@@ -814,14 +808,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Marié(e) civilement</t>
+          <t>Marié(e) selon la tradition</t>
         </is>
       </c>
       <c r="D21">
-        <v>28</v>
+        <v>339</v>
       </c>
       <c r="E21">
-        <v>3.3</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="22">
@@ -837,59 +831,13 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Marié(e) religieusement</t>
+          <t>Veuf(ve)</t>
         </is>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E22">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Marié(e) selon la tradition</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>339</v>
-      </c>
-      <c r="E23">
-        <v>40.3</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Statut matrimonial</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Veuf(ve)</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>21</v>
-      </c>
-      <c r="E24">
         <v>2.5</v>
       </c>
     </row>
